--- a/slide_classification/SurGen_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/SurGen_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.321325</v>
+        <v>0.240115</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.424676</v>
+        <v>0.330358</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.192392</v>
+        <v>0.21366</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8640640000000001</v>
+        <v>0.973319</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.796005</v>
+        <v>0.74502</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -729,10 +729,10 @@
         <v>0.551755</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.581353</v>
+        <v>0.495078</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -772,10 +772,10 @@
         <v>0.062588</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.592996</v>
+        <v>0.387075</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.921107</v>
+        <v>0.880978</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.880396</v>
+        <v>0.887556</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0.000346</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.494645</v>
+        <v>0.581001</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.160782</v>
+        <v>0.08529</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.322872</v>
+        <v>0.217821</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.611777</v>
+        <v>0.694299</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.747227</v>
+        <v>0.830056</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.532246</v>
+        <v>0.522523</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>1e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.482447</v>
+        <v>0.577637</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.413504</v>
+        <v>0.463169</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.219303</v>
+        <v>0.142665</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.401363</v>
+        <v>0.412848</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.407636</v>
+        <v>0.404975</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.403868</v>
+        <v>0.244689</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.443202</v>
+        <v>0.36987</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5622819999999999</v>
+        <v>0.612801</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.618847</v>
+        <v>0.702074</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.726683</v>
+        <v>0.952128</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         <v>0.015554</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.435997</v>
+        <v>0.577574</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1632,10 +1632,10 @@
         <v>0.210808</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.446147</v>
+        <v>0.667678</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.593547</v>
+        <v>0.935561</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.901397</v>
+        <v>0.978224</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.320045</v>
+        <v>0.299316</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.402391</v>
+        <v>0.356728</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1847,10 +1847,10 @@
         <v>1e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.177338</v>
+        <v>0.500321</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2635</v>
+        <v>0.366211</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.264146</v>
+        <v>0.295195</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.609757</v>
+        <v>0.615003</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.333825</v>
+        <v>0.323129</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.648446</v>
+        <v>0.750982</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.269054</v>
+        <v>0.132527</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.321278</v>
+        <v>0.135514</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.427144</v>
+        <v>0.364943</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2234,10 +2234,10 @@
         <v>0.00044</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.520706</v>
+        <v>0.390753</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.408273</v>
+        <v>0.467781</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0.516549</v>
+        <v>0.551443</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.742811</v>
+        <v>0.717477</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.94319</v>
+        <v>0.8692029999999999</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5042</v>
+        <v>0.673558</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2492,10 +2492,10 @@
         <v>0.000172</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.469185</v>
+        <v>0.519135</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.401681</v>
+        <v>0.490639</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.375902</v>
+        <v>0.281166</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.28737</v>
+        <v>0.391865</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.591037</v>
+        <v>0.558735</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2707,10 +2707,10 @@
         <v>0.000348</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.455145</v>
+        <v>0.586925</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.544801</v>
+        <v>0.62605</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.218096</v>
+        <v>0.431908</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2836,10 +2836,10 @@
         <v>0.002271</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0.466841</v>
+        <v>0.541614</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.303602</v>
+        <v>0.313515</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0.567987</v>
+        <v>0.54879</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.373676</v>
+        <v>0.314963</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.208762</v>
+        <v>0.232983</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.610664</v>
+        <v>0.59309</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.217553</v>
+        <v>0.263761</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0.30284</v>
+        <v>0.446604</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.245913</v>
+        <v>0.213406</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3223,10 +3223,10 @@
         <v>0.005567</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5813700000000001</v>
+        <v>0.484249</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.350241</v>
+        <v>0.351606</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.424681</v>
+        <v>0.444383</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.519865</v>
+        <v>0.553768</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.259508</v>
+        <v>0.243155</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.258471</v>
+        <v>0.236</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3484,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.687868</v>
+        <v>0.66852</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0.854229</v>
+        <v>0.749483</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.355237</v>
+        <v>0.350343</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.596256</v>
+        <v>0.5086039999999999</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3653,10 +3653,10 @@
         <v>0.00122</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.546349</v>
+        <v>0.458282</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.32558</v>
+        <v>0.307236</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.3412</v>
+        <v>0.366125</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.221934</v>
+        <v>0.137993</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.840763</v>
+        <v>0.835748</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.885182</v>
+        <v>0.881729</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.620408</v>
+        <v>0.600228</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.371686</v>
+        <v>0.410641</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.373924</v>
+        <v>0.349302</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4040,10 +4040,10 @@
         <v>0.19878</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.497258</v>
+        <v>0.524136</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.342296</v>
+        <v>0.294975</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4126,10 +4126,10 @@
         <v>0.29174</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.501395</v>
+        <v>0.399653</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.404658</v>
+        <v>0.479945</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.216035</v>
+        <v>0.253194</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.281911</v>
+        <v>0.317783</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>0.263824</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0.473247</v>
+        <v>0.699388</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.248479</v>
+        <v>0.205202</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.289701</v>
+        <v>0.419816</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.226452</v>
+        <v>0.251305</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.259146</v>
+        <v>0.327532</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.315762</v>
+        <v>0.371455</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.315686</v>
+        <v>0.283543</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0.57333</v>
+        <v>0.545772</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0.313922</v>
+        <v>0.33864</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.818546</v>
+        <v>0.755602</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.426982</v>
+        <v>0.357112</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.558527</v>
+        <v>0.50145</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.389426</v>
+        <v>0.330484</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>0.593627</v>
+        <v>0.595365</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.317335</v>
+        <v>0.281612</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.386856</v>
+        <v>0.41862</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.291738</v>
+        <v>0.283579</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5029,10 +5029,10 @@
         <v>0.012643</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.550222</v>
+        <v>0.488689</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>0.442474</v>
+        <v>0.491819</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.398699</v>
+        <v>0.420579</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>0.420224</v>
+        <v>0.43773</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.209442</v>
+        <v>0.260197</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.35344</v>
+        <v>0.462172</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.289929</v>
+        <v>0.39509</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.395097</v>
+        <v>0.379312</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.449604</v>
+        <v>0.305753</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.335169</v>
+        <v>0.259979</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.464858</v>
+        <v>0.335215</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.361357</v>
+        <v>0.241587</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5545,10 +5545,10 @@
         <v>0.011234</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.480582</v>
+        <v>0.500988</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.252978</v>
+        <v>0.22029</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.421772</v>
+        <v>0.255285</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.653729</v>
+        <v>0.576628</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.223041</v>
+        <v>0.206079</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.253938</v>
+        <v>0.300533</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.460492</v>
+        <v>0.37934</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.425285</v>
+        <v>0.331683</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.414857</v>
+        <v>0.260146</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.335172</v>
+        <v>0.335517</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.324265</v>
+        <v>0.29606</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.453727</v>
+        <v>0.379983</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0.548686</v>
+        <v>0.502522</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.452694</v>
+        <v>0.453131</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.423547</v>
+        <v>0.220682</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.332268</v>
+        <v>0.29311</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.307103</v>
+        <v>0.215181</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.273314</v>
+        <v>0.224484</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.286844</v>
+        <v>0.220073</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.369577</v>
+        <v>0.374121</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.362357</v>
+        <v>0.307673</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.274089</v>
+        <v>0.254475</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.324765</v>
+        <v>0.210939</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.440536</v>
+        <v>0.444343</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.248996</v>
+        <v>0.214784</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.410877</v>
+        <v>0.354221</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6663,10 +6663,10 @@
         <v>0.000949</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.5234799999999999</v>
+        <v>0.292568</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.349024</v>
+        <v>0.36707</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.186491</v>
+        <v>0.198848</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.363427</v>
+        <v>0.416354</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0.589282</v>
+        <v>0.573914</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.282147</v>
+        <v>0.221766</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.380775</v>
+        <v>0.368782</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6964,10 +6964,10 @@
         <v>0.396925</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.430657</v>
+        <v>0.6177319999999999</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.401741</v>
+        <v>0.401888</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.365182</v>
+        <v>0.344509</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.392377</v>
+        <v>0.375452</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.408292</v>
+        <v>0.288713</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.307779</v>
+        <v>0.34461</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -20641,7 +20641,7 @@
         <v>0</v>
       </c>
       <c r="G470" t="n">
-        <v>0.434322</v>
+        <v>0.374969</v>
       </c>
       <c r="H470" t="n">
         <v>0</v>
@@ -20684,7 +20684,7 @@
         <v>0</v>
       </c>
       <c r="G471" t="n">
-        <v>0.47149</v>
+        <v>0.481551</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -20727,7 +20727,7 @@
         <v>0</v>
       </c>
       <c r="G472" t="n">
-        <v>0.154964</v>
+        <v>0.340083</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -20770,7 +20770,7 @@
         <v>0</v>
       </c>
       <c r="G473" t="n">
-        <v>0.233371</v>
+        <v>0.312681</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -20813,7 +20813,7 @@
         <v>0</v>
       </c>
       <c r="G474" t="n">
-        <v>0.467681</v>
+        <v>0.433394</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -20853,10 +20853,10 @@
         <v>2.6e-05</v>
       </c>
       <c r="F475" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G475" t="n">
-        <v>0.683693</v>
+        <v>0.479512</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -20899,7 +20899,7 @@
         <v>1</v>
       </c>
       <c r="G476" t="n">
-        <v>0.83503</v>
+        <v>0.537558</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -20942,7 +20942,7 @@
         <v>0</v>
       </c>
       <c r="G477" t="n">
-        <v>0.441183</v>
+        <v>0.469292</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -20985,7 +20985,7 @@
         <v>1</v>
       </c>
       <c r="G478" t="n">
-        <v>0.598906</v>
+        <v>0.520221</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -21028,7 +21028,7 @@
         <v>1</v>
       </c>
       <c r="G479" t="n">
-        <v>0.538065</v>
+        <v>0.517861</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
@@ -21071,7 +21071,7 @@
         <v>1</v>
       </c>
       <c r="G480" t="n">
-        <v>0.725249</v>
+        <v>0.57539</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -21114,7 +21114,7 @@
         <v>0</v>
       </c>
       <c r="G481" t="n">
-        <v>0.379699</v>
+        <v>0.458116</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -21157,7 +21157,7 @@
         <v>1</v>
       </c>
       <c r="G482" t="n">
-        <v>0.574441</v>
+        <v>0.594289</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -21200,7 +21200,7 @@
         <v>0</v>
       </c>
       <c r="G483" t="n">
-        <v>0.38499</v>
+        <v>0.498534</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -21243,7 +21243,7 @@
         <v>0</v>
       </c>
       <c r="G484" t="n">
-        <v>0.360082</v>
+        <v>0.439167</v>
       </c>
       <c r="H484" t="n">
         <v>0</v>
@@ -21286,7 +21286,7 @@
         <v>0</v>
       </c>
       <c r="G485" t="n">
-        <v>0.333391</v>
+        <v>0.41665</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -21326,10 +21326,10 @@
         <v>0.00029</v>
       </c>
       <c r="F486" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G486" t="n">
-        <v>0.5044689999999999</v>
+        <v>0.476829</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -21372,7 +21372,7 @@
         <v>0</v>
       </c>
       <c r="G487" t="n">
-        <v>0.42705</v>
+        <v>0.469678</v>
       </c>
       <c r="H487" t="n">
         <v>1</v>
@@ -21415,7 +21415,7 @@
         <v>0</v>
       </c>
       <c r="G488" t="n">
-        <v>0.258167</v>
+        <v>0.33277</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -21458,7 +21458,7 @@
         <v>1</v>
       </c>
       <c r="G489" t="n">
-        <v>0.703467</v>
+        <v>0.586041</v>
       </c>
       <c r="H489" t="n">
         <v>0</v>
@@ -21501,7 +21501,7 @@
         <v>0</v>
       </c>
       <c r="G490" t="n">
-        <v>0.331597</v>
+        <v>0.438445</v>
       </c>
       <c r="H490" t="n">
         <v>0</v>
@@ -21544,7 +21544,7 @@
         <v>0</v>
       </c>
       <c r="G491" t="n">
-        <v>0.360866</v>
+        <v>0.379321</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -21587,7 +21587,7 @@
         <v>0</v>
       </c>
       <c r="G492" t="n">
-        <v>0.34067</v>
+        <v>0.430394</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -21630,7 +21630,7 @@
         <v>0</v>
       </c>
       <c r="G493" t="n">
-        <v>0.433629</v>
+        <v>0.455039</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>0</v>
       </c>
       <c r="G494" t="n">
-        <v>0.187892</v>
+        <v>0.259538</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -21716,7 +21716,7 @@
         <v>0</v>
       </c>
       <c r="G495" t="n">
-        <v>0.286656</v>
+        <v>0.342279</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -21759,7 +21759,7 @@
         <v>0</v>
       </c>
       <c r="G496" t="n">
-        <v>0.286619</v>
+        <v>0.442986</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -21799,10 +21799,10 @@
         <v>7e-06</v>
       </c>
       <c r="F497" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G497" t="n">
-        <v>0.373346</v>
+        <v>0.52683</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -21845,7 +21845,7 @@
         <v>1</v>
       </c>
       <c r="G498" t="n">
-        <v>0.839303</v>
+        <v>0.555691</v>
       </c>
       <c r="H498" t="n">
         <v>0</v>
@@ -21888,7 +21888,7 @@
         <v>1</v>
       </c>
       <c r="G499" t="n">
-        <v>0.84521</v>
+        <v>0.581047</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -21931,7 +21931,7 @@
         <v>0</v>
       </c>
       <c r="G500" t="n">
-        <v>0.336081</v>
+        <v>0.428984</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -21974,7 +21974,7 @@
         <v>0</v>
       </c>
       <c r="G501" t="n">
-        <v>0.265549</v>
+        <v>0.472826</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -22017,7 +22017,7 @@
         <v>1</v>
       </c>
       <c r="G502" t="n">
-        <v>0.574071</v>
+        <v>0.575509</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="G503" t="n">
-        <v>0.574959</v>
+        <v>0.5426299999999999</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -22103,7 +22103,7 @@
         <v>0</v>
       </c>
       <c r="G504" t="n">
-        <v>0.268582</v>
+        <v>0.461677</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -22143,10 +22143,10 @@
         <v>0.000192</v>
       </c>
       <c r="F505" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G505" t="n">
-        <v>0.511191</v>
+        <v>0.484767</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -22189,7 +22189,7 @@
         <v>1</v>
       </c>
       <c r="G506" t="n">
-        <v>0.739511</v>
+        <v>0.621814</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -22229,10 +22229,10 @@
         <v>0.170565</v>
       </c>
       <c r="F507" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G507" t="n">
-        <v>0.461254</v>
+        <v>0.520357</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -22275,7 +22275,7 @@
         <v>0</v>
       </c>
       <c r="G508" t="n">
-        <v>0.178406</v>
+        <v>0.302215</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -22318,7 +22318,7 @@
         <v>1</v>
       </c>
       <c r="G509" t="n">
-        <v>0.540924</v>
+        <v>0.554148</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -22361,7 +22361,7 @@
         <v>0</v>
       </c>
       <c r="G510" t="n">
-        <v>0.373639</v>
+        <v>0.367438</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -22404,7 +22404,7 @@
         <v>0</v>
       </c>
       <c r="G511" t="n">
-        <v>0.382697</v>
+        <v>0.396052</v>
       </c>
       <c r="H511" t="n">
         <v>0</v>
@@ -22444,10 +22444,10 @@
         <v>9.399999999999999e-05</v>
       </c>
       <c r="F512" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G512" t="n">
-        <v>0.609952</v>
+        <v>0.485154</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -22487,10 +22487,10 @@
         <v>0.001081</v>
       </c>
       <c r="F513" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>0.486189</v>
+        <v>0.538686</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -22533,7 +22533,7 @@
         <v>1</v>
       </c>
       <c r="G514" t="n">
-        <v>0.713127</v>
+        <v>0.655443</v>
       </c>
       <c r="H514" t="n">
         <v>1</v>
@@ -22576,7 +22576,7 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0.765892</v>
+        <v>0.632175</v>
       </c>
       <c r="H515" t="n">
         <v>0</v>
@@ -22619,7 +22619,7 @@
         <v>1</v>
       </c>
       <c r="G516" t="n">
-        <v>0.721724</v>
+        <v>0.5374679999999999</v>
       </c>
       <c r="H516" t="n">
         <v>1</v>
@@ -22662,7 +22662,7 @@
         <v>1</v>
       </c>
       <c r="G517" t="n">
-        <v>0.5828989999999999</v>
+        <v>0.506894</v>
       </c>
       <c r="H517" t="n">
         <v>1</v>
@@ -22705,7 +22705,7 @@
         <v>0</v>
       </c>
       <c r="G518" t="n">
-        <v>0.396005</v>
+        <v>0.457547</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -22748,7 +22748,7 @@
         <v>0</v>
       </c>
       <c r="G519" t="n">
-        <v>0.475745</v>
+        <v>0.466796</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -22791,7 +22791,7 @@
         <v>0</v>
       </c>
       <c r="G520" t="n">
-        <v>0.214912</v>
+        <v>0.23644</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -22834,7 +22834,7 @@
         <v>1</v>
       </c>
       <c r="G521" t="n">
-        <v>0.640676</v>
+        <v>0.609156</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -22877,7 +22877,7 @@
         <v>0</v>
       </c>
       <c r="G522" t="n">
-        <v>0.291484</v>
+        <v>0.494152</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -22920,7 +22920,7 @@
         <v>0</v>
       </c>
       <c r="G523" t="n">
-        <v>0.317319</v>
+        <v>0.460059</v>
       </c>
       <c r="H523" t="n">
         <v>0</v>
@@ -22963,7 +22963,7 @@
         <v>0</v>
       </c>
       <c r="G524" t="n">
-        <v>0.285977</v>
+        <v>0.330515</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -23006,7 +23006,7 @@
         <v>0</v>
       </c>
       <c r="G525" t="n">
-        <v>0.235779</v>
+        <v>0.452422</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -23049,7 +23049,7 @@
         <v>0</v>
       </c>
       <c r="G526" t="n">
-        <v>0.232294</v>
+        <v>0.340475</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -23092,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="G527" t="n">
-        <v>0.403268</v>
+        <v>0.424213</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -23132,10 +23132,10 @@
         <v>0.000132</v>
       </c>
       <c r="F528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G528" t="n">
-        <v>0.424496</v>
+        <v>0.526299</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -23178,7 +23178,7 @@
         <v>0</v>
       </c>
       <c r="G529" t="n">
-        <v>0.192951</v>
+        <v>0.326451</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>1</v>
       </c>
       <c r="G530" t="n">
-        <v>0.621465</v>
+        <v>0.522721</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -23264,7 +23264,7 @@
         <v>0</v>
       </c>
       <c r="G531" t="n">
-        <v>0.403295</v>
+        <v>0.419279</v>
       </c>
       <c r="H531" t="n">
         <v>0</v>
@@ -23307,7 +23307,7 @@
         <v>0</v>
       </c>
       <c r="G532" t="n">
-        <v>0.100163</v>
+        <v>0.331657</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -23350,7 +23350,7 @@
         <v>0</v>
       </c>
       <c r="G533" t="n">
-        <v>0.21608</v>
+        <v>0.425449</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -23393,7 +23393,7 @@
         <v>0</v>
       </c>
       <c r="G534" t="n">
-        <v>0.154095</v>
+        <v>0.366889</v>
       </c>
       <c r="H534" t="n">
         <v>0</v>
@@ -23433,10 +23433,10 @@
         <v>0.004257</v>
       </c>
       <c r="F535" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G535" t="n">
-        <v>0.463876</v>
+        <v>0.504598</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -23479,7 +23479,7 @@
         <v>0</v>
       </c>
       <c r="G536" t="n">
-        <v>0.198751</v>
+        <v>0.387367</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -23522,7 +23522,7 @@
         <v>0</v>
       </c>
       <c r="G537" t="n">
-        <v>0.329956</v>
+        <v>0.478336</v>
       </c>
       <c r="H537" t="n">
         <v>0</v>
@@ -23565,7 +23565,7 @@
         <v>0</v>
       </c>
       <c r="G538" t="n">
-        <v>0.222472</v>
+        <v>0.371859</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -23608,7 +23608,7 @@
         <v>0</v>
       </c>
       <c r="G539" t="n">
-        <v>0.371753</v>
+        <v>0.476563</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -23651,7 +23651,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>0.7683</v>
+        <v>0.5343869999999999</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -23694,7 +23694,7 @@
         <v>0</v>
       </c>
       <c r="G541" t="n">
-        <v>0.267101</v>
+        <v>0.399745</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -23737,7 +23737,7 @@
         <v>1</v>
       </c>
       <c r="G542" t="n">
-        <v>0.522645</v>
+        <v>0.528547</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -23777,10 +23777,10 @@
         <v>0.005254</v>
       </c>
       <c r="F543" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G543" t="n">
-        <v>0.50457</v>
+        <v>0.467273</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -23823,7 +23823,7 @@
         <v>0</v>
       </c>
       <c r="G544" t="n">
-        <v>0.479768</v>
+        <v>0.491947</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -23866,7 +23866,7 @@
         <v>0</v>
       </c>
       <c r="G545" t="n">
-        <v>0.273317</v>
+        <v>0.369266</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -23909,7 +23909,7 @@
         <v>0</v>
       </c>
       <c r="G546" t="n">
-        <v>0.212358</v>
+        <v>0.442774</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -23949,10 +23949,10 @@
         <v>0.00242</v>
       </c>
       <c r="F547" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G547" t="n">
-        <v>0.499035</v>
+        <v>0.514479</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -23995,7 +23995,7 @@
         <v>0</v>
       </c>
       <c r="G548" t="n">
-        <v>0.289814</v>
+        <v>0.409827</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -24038,7 +24038,7 @@
         <v>1</v>
       </c>
       <c r="G549" t="n">
-        <v>0.56108</v>
+        <v>0.529818</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -24081,7 +24081,7 @@
         <v>0</v>
       </c>
       <c r="G550" t="n">
-        <v>0.2402</v>
+        <v>0.388021</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -24124,7 +24124,7 @@
         <v>0</v>
       </c>
       <c r="G551" t="n">
-        <v>0.391374</v>
+        <v>0.438249</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -24167,7 +24167,7 @@
         <v>0</v>
       </c>
       <c r="G552" t="n">
-        <v>0.225739</v>
+        <v>0.422988</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -24210,7 +24210,7 @@
         <v>0</v>
       </c>
       <c r="G553" t="n">
-        <v>0.302042</v>
+        <v>0.400986</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -24253,7 +24253,7 @@
         <v>1</v>
       </c>
       <c r="G554" t="n">
-        <v>0.7616270000000001</v>
+        <v>0.536451</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="G555" t="n">
-        <v>0.488717</v>
+        <v>0.453923</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -24339,7 +24339,7 @@
         <v>0</v>
       </c>
       <c r="G556" t="n">
-        <v>0.424045</v>
+        <v>0.454038</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -24382,7 +24382,7 @@
         <v>1</v>
       </c>
       <c r="G557" t="n">
-        <v>0.535524</v>
+        <v>0.501443</v>
       </c>
       <c r="H557" t="n">
         <v>0</v>
@@ -24425,7 +24425,7 @@
         <v>0</v>
       </c>
       <c r="G558" t="n">
-        <v>0.191747</v>
+        <v>0.422717</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>0</v>
       </c>
       <c r="G559" t="n">
-        <v>0.359012</v>
+        <v>0.386443</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -24508,10 +24508,10 @@
         <v>0.00233</v>
       </c>
       <c r="F560" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G560" t="n">
-        <v>0.717744</v>
+        <v>0.454511</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -24554,7 +24554,7 @@
         <v>0</v>
       </c>
       <c r="G561" t="n">
-        <v>0.228046</v>
+        <v>0.420359</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -24597,7 +24597,7 @@
         <v>0</v>
       </c>
       <c r="G562" t="n">
-        <v>0.48956</v>
+        <v>0.395572</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -24640,7 +24640,7 @@
         <v>0</v>
       </c>
       <c r="G563" t="n">
-        <v>0.392606</v>
+        <v>0.467259</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -24683,7 +24683,7 @@
         <v>0</v>
       </c>
       <c r="G564" t="n">
-        <v>0.288018</v>
+        <v>0.46283</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -24726,7 +24726,7 @@
         <v>1</v>
       </c>
       <c r="G565" t="n">
-        <v>0.770841</v>
+        <v>0.52545</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -24769,7 +24769,7 @@
         <v>1</v>
       </c>
       <c r="G566" t="n">
-        <v>0.545757</v>
+        <v>0.514385</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -24812,7 +24812,7 @@
         <v>0</v>
       </c>
       <c r="G567" t="n">
-        <v>0.189017</v>
+        <v>0.353059</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -24855,7 +24855,7 @@
         <v>0</v>
       </c>
       <c r="G568" t="n">
-        <v>0.199303</v>
+        <v>0.39377</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -24895,10 +24895,10 @@
         <v>1.9e-05</v>
       </c>
       <c r="F569" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G569" t="n">
-        <v>0.489191</v>
+        <v>0.519894</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -24941,7 +24941,7 @@
         <v>0</v>
       </c>
       <c r="G570" t="n">
-        <v>0.417731</v>
+        <v>0.482384</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
         <v>0</v>
       </c>
       <c r="G571" t="n">
-        <v>0.143146</v>
+        <v>0.39938</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -25027,7 +25027,7 @@
         <v>0</v>
       </c>
       <c r="G572" t="n">
-        <v>0.302837</v>
+        <v>0.407066</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="G573" t="n">
-        <v>0.202204</v>
+        <v>0.410968</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -25113,7 +25113,7 @@
         <v>0</v>
       </c>
       <c r="G574" t="n">
-        <v>0.267464</v>
+        <v>0.435894</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="G575" t="n">
-        <v>0.364611</v>
+        <v>0.434434</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -25199,7 +25199,7 @@
         <v>0</v>
       </c>
       <c r="G576" t="n">
-        <v>0.284555</v>
+        <v>0.447707</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -25239,10 +25239,10 @@
         <v>0.00455</v>
       </c>
       <c r="F577" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G577" t="n">
-        <v>0.417704</v>
+        <v>0.525795</v>
       </c>
       <c r="H577" t="n">
         <v>0</v>
@@ -25282,10 +25282,10 @@
         <v>7e-06</v>
       </c>
       <c r="F578" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G578" t="n">
-        <v>0.542556</v>
+        <v>0.472089</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>1</v>
       </c>
       <c r="G579" t="n">
-        <v>0.598739</v>
+        <v>0.514861</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -25368,10 +25368,10 @@
         <v>0.001176</v>
       </c>
       <c r="F580" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G580" t="n">
-        <v>0.455285</v>
+        <v>0.514533</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -25414,7 +25414,7 @@
         <v>0</v>
       </c>
       <c r="G581" t="n">
-        <v>0.363937</v>
+        <v>0.449889</v>
       </c>
       <c r="H581" t="n">
         <v>0</v>
@@ -25457,7 +25457,7 @@
         <v>0</v>
       </c>
       <c r="G582" t="n">
-        <v>0.442373</v>
+        <v>0.499533</v>
       </c>
       <c r="H582" t="n">
         <v>0</v>
@@ -25500,7 +25500,7 @@
         <v>0</v>
       </c>
       <c r="G583" t="n">
-        <v>0.331635</v>
+        <v>0.413789</v>
       </c>
       <c r="H583" t="n">
         <v>0</v>
@@ -25543,7 +25543,7 @@
         <v>0</v>
       </c>
       <c r="G584" t="n">
-        <v>0.467352</v>
+        <v>0.430695</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -25586,7 +25586,7 @@
         <v>0</v>
       </c>
       <c r="G585" t="n">
-        <v>0.146142</v>
+        <v>0.364045</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -25629,7 +25629,7 @@
         <v>0</v>
       </c>
       <c r="G586" t="n">
-        <v>0.355224</v>
+        <v>0.376561</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -25672,7 +25672,7 @@
         <v>0</v>
       </c>
       <c r="G587" t="n">
-        <v>0.320958</v>
+        <v>0.472473</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="G588" t="n">
-        <v>0.324453</v>
+        <v>0.405016</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -25755,10 +25755,10 @@
         <v>1e-06</v>
       </c>
       <c r="F589" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G589" t="n">
-        <v>0.526506</v>
+        <v>0.468247</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -25801,7 +25801,7 @@
         <v>0</v>
       </c>
       <c r="G590" t="n">
-        <v>0.377862</v>
+        <v>0.396953</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -25844,7 +25844,7 @@
         <v>0</v>
       </c>
       <c r="G591" t="n">
-        <v>0.319835</v>
+        <v>0.406528</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -25887,7 +25887,7 @@
         <v>0</v>
       </c>
       <c r="G592" t="n">
-        <v>0.470986</v>
+        <v>0.433597</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -25927,10 +25927,10 @@
         <v>0.924056</v>
       </c>
       <c r="F593" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G593" t="n">
-        <v>0.5712390000000001</v>
+        <v>0.460047</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -25970,10 +25970,10 @@
         <v>3.7e-05</v>
       </c>
       <c r="F594" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G594" t="n">
-        <v>0.59579</v>
+        <v>0.452465</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -26016,7 +26016,7 @@
         <v>0</v>
       </c>
       <c r="G595" t="n">
-        <v>0.369839</v>
+        <v>0.430608</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -26059,7 +26059,7 @@
         <v>0</v>
       </c>
       <c r="G596" t="n">
-        <v>0.171761</v>
+        <v>0.356211</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -26099,10 +26099,10 @@
         <v>1.6e-05</v>
       </c>
       <c r="F597" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G597" t="n">
-        <v>0.6433410000000001</v>
+        <v>0.457949</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -26142,10 +26142,10 @@
         <v>0.057767</v>
       </c>
       <c r="F598" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G598" t="n">
-        <v>0.519323</v>
+        <v>0.483159</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -26188,7 +26188,7 @@
         <v>0</v>
       </c>
       <c r="G599" t="n">
-        <v>0.470491</v>
+        <v>0.400685</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -26231,7 +26231,7 @@
         <v>0</v>
       </c>
       <c r="G600" t="n">
-        <v>0.219577</v>
+        <v>0.384754</v>
       </c>
       <c r="H600" t="n">
         <v>0</v>
@@ -26274,7 +26274,7 @@
         <v>0</v>
       </c>
       <c r="G601" t="n">
-        <v>0.412466</v>
+        <v>0.408614</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -26317,7 +26317,7 @@
         <v>0</v>
       </c>
       <c r="G602" t="n">
-        <v>0.240263</v>
+        <v>0.415935</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -26360,7 +26360,7 @@
         <v>0</v>
       </c>
       <c r="G603" t="n">
-        <v>0.420418</v>
+        <v>0.46677</v>
       </c>
       <c r="H603" t="n">
         <v>0</v>
@@ -26403,7 +26403,7 @@
         <v>0</v>
       </c>
       <c r="G604" t="n">
-        <v>0.341985</v>
+        <v>0.426773</v>
       </c>
       <c r="H604" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
         <v>0</v>
       </c>
       <c r="G605" t="n">
-        <v>0.262883</v>
+        <v>0.388045</v>
       </c>
       <c r="H605" t="n">
         <v>0</v>
@@ -26489,7 +26489,7 @@
         <v>0</v>
       </c>
       <c r="G606" t="n">
-        <v>0.271365</v>
+        <v>0.407328</v>
       </c>
       <c r="H606" t="n">
         <v>0</v>
@@ -26532,7 +26532,7 @@
         <v>0</v>
       </c>
       <c r="G607" t="n">
-        <v>0.317117</v>
+        <v>0.412662</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -26575,7 +26575,7 @@
         <v>0</v>
       </c>
       <c r="G608" t="n">
-        <v>0.410509</v>
+        <v>0.465687</v>
       </c>
       <c r="H608" t="n">
         <v>0</v>
@@ -26618,7 +26618,7 @@
         <v>0</v>
       </c>
       <c r="G609" t="n">
-        <v>0.257763</v>
+        <v>0.464685</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -26661,7 +26661,7 @@
         <v>0</v>
       </c>
       <c r="G610" t="n">
-        <v>0.248755</v>
+        <v>0.370719</v>
       </c>
       <c r="H610" t="n">
         <v>0</v>
@@ -26701,10 +26701,10 @@
         <v>0.044152</v>
       </c>
       <c r="F611" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G611" t="n">
-        <v>0.577233</v>
+        <v>0.408596</v>
       </c>
       <c r="H611" t="n">
         <v>0</v>
@@ -26747,7 +26747,7 @@
         <v>0</v>
       </c>
       <c r="G612" t="n">
-        <v>0.275812</v>
+        <v>0.391713</v>
       </c>
       <c r="H612" t="n">
         <v>0</v>
@@ -26790,7 +26790,7 @@
         <v>0</v>
       </c>
       <c r="G613" t="n">
-        <v>0.192354</v>
+        <v>0.44133</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -26833,7 +26833,7 @@
         <v>0</v>
       </c>
       <c r="G614" t="n">
-        <v>0.334301</v>
+        <v>0.443119</v>
       </c>
       <c r="H614" t="n">
         <v>0</v>
@@ -26876,7 +26876,7 @@
         <v>0</v>
       </c>
       <c r="G615" t="n">
-        <v>0.334734</v>
+        <v>0.466993</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -26919,7 +26919,7 @@
         <v>1</v>
       </c>
       <c r="G616" t="n">
-        <v>0.947074</v>
+        <v>0.623151</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>0</v>
       </c>
       <c r="G617" t="n">
-        <v>0.159112</v>
+        <v>0.362691</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -27005,7 +27005,7 @@
         <v>0</v>
       </c>
       <c r="G618" t="n">
-        <v>0.148686</v>
+        <v>0.347687</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -27048,7 +27048,7 @@
         <v>0</v>
       </c>
       <c r="G619" t="n">
-        <v>0.235867</v>
+        <v>0.373656</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -27088,10 +27088,10 @@
         <v>4e-06</v>
       </c>
       <c r="F620" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G620" t="n">
-        <v>0.500525</v>
+        <v>0.477001</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -27131,10 +27131,10 @@
         <v>0.000845</v>
       </c>
       <c r="F621" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0.373789</v>
+        <v>0.506224</v>
       </c>
       <c r="H621" t="n">
         <v>0</v>
@@ -27174,10 +27174,10 @@
         <v>9.6e-05</v>
       </c>
       <c r="F622" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G622" t="n">
-        <v>0.518106</v>
+        <v>0.458531</v>
       </c>
       <c r="H622" t="n">
         <v>0</v>
@@ -27220,7 +27220,7 @@
         <v>0</v>
       </c>
       <c r="G623" t="n">
-        <v>0.373633</v>
+        <v>0.383867</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
